--- a/apps/nuxt/i18n/i18n.xlsx
+++ b/apps/nuxt/i18n/i18n.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11625" uniqueCount="10633">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11631" uniqueCount="10639">
   <si>
     <t>key</t>
   </si>
@@ -21488,6 +21488,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t xml:space="preserve">基于“艾宾浩斯遗忘曲线”设计，系统会根据你的记忆情况，自动安排最合适的复习时间。 </t>
     </r>
     <r>
@@ -21535,6 +21542,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>Designed based on the "Ebbinghaus Forgetting Curve", the system will automatically arrange the most suitable review time according to your memory status.</t>
     </r>
     <r>
@@ -21582,6 +21596,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>「エビングハウスの忘却曲線」に基づいて設計されたシステムは、あなたの記憶状況に応じて最適な復習時間を自動的に手配します。</t>
     </r>
     <r>
@@ -21629,6 +21650,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>"에빙하우스 망각 곡선"을 기반으로 설계된 시스템은 사용자의 기억 상태에 따라 가장 적합한 복습 시간을 자동으로 배정합니다.</t>
     </r>
     <r>
@@ -21676,6 +21704,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>Diseñado basado en la "Curva de Olvido de Ebbinghaus", el sistema organizará automáticamente el tiempo de repaso más adecuado según tu estado de memoria.</t>
     </r>
     <r>
@@ -21723,6 +21758,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>Projetado com base na "Curva do Esquecimento de Ebbinghaus", o sistema organizará automaticamente o tempo de revisão mais adequado de acordo com o seu estado de memória.</t>
     </r>
     <r>
@@ -21770,6 +21812,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>Entwickelt auf Basis der "Ebbinghaus-Vergessenskurve", arrangiert das System automatisch die optimalste Wiederholungszeit entsprechend deinem Gedächtniszustand.</t>
     </r>
     <r>
@@ -21817,6 +21866,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>Conçu sur la base de la "Courbe d'Oubli d'Ebbinghaus", le système organisera automatiquement le temps de révision le plus adapté en fonction de votre état de mémoire.</t>
     </r>
     <r>
@@ -21864,6 +21920,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>Разработанный на основе "Кривой забывания Эббингауза", система автоматически подбирает наиболее подходящее время для повторения в зависимости от состояния вашей памяти.</t>
     </r>
     <r>
@@ -21911,6 +21974,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>ออกแบบตาม "เส้นโค้งการลืมของเอบบิงเฮาส์" ระบบจะจัดระยะเวลาทบทวนที่เหมาะสมที่สุดโดยอัตโนมัติตามสถานะความจำของคุณ</t>
     </r>
     <r>
@@ -21958,6 +22028,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>Được thiết kế dựa trên "Đường cong Quên của Ebbinghaus", hệ thống sẽ tự động sắp xếp thời gian ôn tập phù hợp nhất theo tình trạng trí nhớ của bạn.</t>
     </r>
     <r>
@@ -22005,6 +22082,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>Dirancang berdasarkan "Kurva Lupa Ebbinghaus", sistem akan secara otomatis mengatur waktu ulasan yang paling sesuai sesuai dengan status ingatan Anda.</t>
     </r>
     <r>
@@ -22052,6 +22136,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>Розроблений на основі "Кривої забування Еббінгауза", система автоматично підбирає найбільш підходящий час для повторення залежно від стану вашої пам'яті.</t>
     </r>
     <r>
@@ -22099,6 +22190,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>基於「艾賓浩斯遺忘曲線」設計，系統會根據你的記憶情況，自動安排最合適的複習時間。</t>
     </r>
     <r>
@@ -32557,6 +32655,24 @@
   <si>
     <t>這一發現對現代科學產生了深遠的影響。</t>
   </si>
+  <si>
+    <t>create_copy</t>
+  </si>
+  <si>
+    <t>创建副本</t>
+  </si>
+  <si>
+    <t>Create Copy</t>
+  </si>
+  <si>
+    <t>create_copy_to_edit</t>
+  </si>
+  <si>
+    <t>官方资源不可编辑，请先创建副本</t>
+  </si>
+  <si>
+    <t>Official resources are read-only. Please create a copy first.</t>
+  </si>
 </sst>
 </file>
 
@@ -32568,14 +32684,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="23">
-    <font>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
+  <fonts count="22">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -33059,28 +33168,31 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="42" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -33089,126 +33201,123 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -33595,7 +33704,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:O775"/>
+  <dimension ref="A1:O777"/>
   <sheetFormatPr defaultColWidth="9.64285714285714" defaultRowHeight="17.6"/>
   <cols>
     <col min="1" max="1" width="23.0982142857143" customWidth="1"/>
@@ -70030,11 +70139,33 @@
         <v>10632</v>
       </c>
     </row>
+    <row r="776" spans="1:15">
+      <c r="A776" t="s">
+        <v>10633</v>
+      </c>
+      <c r="B776" t="s">
+        <v>10634</v>
+      </c>
+      <c r="C776" t="s">
+        <v>10635</v>
+      </c>
+    </row>
+    <row r="777" spans="1:15">
+      <c r="A777" t="s">
+        <v>10636</v>
+      </c>
+      <c r="B777" t="s">
+        <v>10637</v>
+      </c>
+      <c r="C777" t="s">
+        <v>10638</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
   <ignoredErrors>
-    <ignoredError sqref="A1:O508 A534:A545 A548:A775" numberStoredAsText="1"/>
+    <ignoredError sqref="A548:A775 A534:A545 A1:O508" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>